--- a/artfynd/A 25707-2025 artfynd.xlsx
+++ b/artfynd/A 25707-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110208745</v>
+        <v>110204754</v>
       </c>
       <c r="B4" t="n">
-        <v>56540</v>
+        <v>95511</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,38 +919,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>221944</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knäsjöberget, Ång</t>
+          <t>Vitberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609794.7675553771</v>
+        <v>609731.5383536966</v>
       </c>
       <c r="R4" t="n">
-        <v>6991471.619591354</v>
+        <v>6991418.164448518</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110208135</v>
+        <v>110208745</v>
       </c>
       <c r="B5" t="n">
-        <v>77258</v>
+        <v>56540</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,34 +1035,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sörlidberget, Ång</t>
+          <t>Knäsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609834.6968590898</v>
+        <v>609794.7675553771</v>
       </c>
       <c r="R5" t="n">
-        <v>6991474.331189074</v>
+        <v>6991471.619591354</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,7 +1131,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110204806</v>
+        <v>110208135</v>
       </c>
       <c r="B6" t="n">
         <v>77258</v>
@@ -1167,14 +1167,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vitberget, Ång</t>
+          <t>Sörlidberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609828.0264708162</v>
+        <v>609834.6968590898</v>
       </c>
       <c r="R6" t="n">
-        <v>6991456.393724103</v>
+        <v>6991474.331189074</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,6 +1240,118 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>110204806</v>
+      </c>
+      <c r="B7" t="n">
+        <v>77258</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vitberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>609828.0264708162</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6991456.393724103</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-10-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-10-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>klara linder</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>klara linder, Emmy Ransgart, Astrid Hedman, Ulf Sperens, Nils Ericson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25707-2025 artfynd.xlsx
+++ b/artfynd/A 25707-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96508231</v>
+        <v>110204292</v>
       </c>
       <c r="B2" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Knäsjöberget, Knäsjöberget, Ång</t>
+          <t>Vitberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609829.7893556312</v>
+        <v>609752</v>
       </c>
       <c r="R2" t="n">
-        <v>6991404.224893535</v>
+        <v>6991378</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,56 +754,50 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johannes Esberg</t>
+          <t>klara linder</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johannes Esberg</t>
+          <t>klara linder, Emmy Ransgart, Astrid Hedman, Ulf Sperens, Nils Ericson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97210938</v>
+        <v>97210992</v>
       </c>
       <c r="B3" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +810,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609746.1152608788</v>
+        <v>609793</v>
       </c>
       <c r="R3" t="n">
-        <v>6991471.338846878</v>
+        <v>6991521</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,19 +843,9 @@
           <t>2021-09-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,50 +873,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110204754</v>
+        <v>96508231</v>
       </c>
       <c r="B4" t="n">
-        <v>95511</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221944</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vitberget, Ång</t>
+          <t>Knäsjöberget, Knäsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609731.5383536966</v>
+        <v>609830</v>
       </c>
       <c r="R4" t="n">
-        <v>6991418.164448518</v>
+        <v>6991405</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,22 +941,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,33 +955,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>klara linder</t>
+          <t>Johannes Esberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>klara linder, Emmy Ransgart, Astrid Hedman, Ulf Sperens, Nils Ericson</t>
+          <t>Johannes Esberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110208745</v>
+        <v>110204806</v>
       </c>
       <c r="B5" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,34 +985,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knäsjöberget, Ång</t>
+          <t>Vitberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609794.7675553771</v>
+        <v>609828</v>
       </c>
       <c r="R5" t="n">
-        <v>6991471.619591354</v>
+        <v>6991456</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,19 +1042,9 @@
           <t>2022-10-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,15 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110208135</v>
+        <v>110204807</v>
       </c>
       <c r="B6" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,14 +1102,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sörlidberget, Ång</t>
+          <t>Vitberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609834.6968590898</v>
+        <v>609835</v>
       </c>
       <c r="R6" t="n">
-        <v>6991474.331189074</v>
+        <v>6991474</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,19 +1139,9 @@
           <t>2022-10-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,15 +1168,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110204806</v>
+        <v>97210978</v>
       </c>
       <c r="B7" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,37 +1179,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vitberget, Ång</t>
+          <t>Bäverklippen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609828.0264708162</v>
+        <v>609753</v>
       </c>
       <c r="R7" t="n">
-        <v>6991456.393724103</v>
+        <v>6991505</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,22 +1236,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,21 +1250,709 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Johannes Esberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johannes Esberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>97210981</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bäverklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>609769</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6991521</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johannes Esberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johannes Esberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>97203540</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bäverklippen, Knäsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>609736</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6991401</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johannes Esberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johannes Esberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>97210938</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bäverklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>609746</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6991471</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johannes Esberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johannes Esberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>110204338</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vitberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>609744</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6991360</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-10-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-10-21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>klara linder</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>klara linder, Emmy Ransgart, Astrid Hedman, Ulf Sperens, Jonas Forsberg, Nils Ericson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>110204377</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vitberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>609795</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6991472</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-10-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-10-21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>klara linder</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
         <is>
           <t>klara linder, Emmy Ransgart, Astrid Hedman, Ulf Sperens, Nils Ericson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>110204754</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vitberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>609732</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6991418</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-10-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-10-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>klara linder</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>klara linder, Emmy Ransgart, Astrid Hedman, Ulf Sperens, Nils Ericson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>110204594</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vitberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>609726</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6991401</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-10-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-10-21</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>klara linder</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>klara linder, Emmy Ransgart, Astrid Hedman, Ulf Sperens, Jonas Forsberg, Nils Ericson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25707-2025 artfynd.xlsx
+++ b/artfynd/A 25707-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110204292</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97210992</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96508231</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110204806</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110204807</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97210978</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,6 +1402,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97210981</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97203540</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1569,6 +1614,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97210938</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1666,6 +1716,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110204338</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1763,6 +1818,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110204377</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110204754</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1953,8 +2018,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110204594</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>